--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260929.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260929.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.64%</t>
+          <t>9.71%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.26%</t>
+          <t>9.24%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>6.47%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.74%</t>
+          <t>5.82%</t>
         </is>
       </c>
     </row>
@@ -704,73 +704,73 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>4.48%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>5,142,000</t>
+          <t>109,122,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>3.98%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>109,122,000</t>
+          <t>604,027,270</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>3.87%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>604,027,270</t>
+          <t>5,142,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>3.87%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.24%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.81%</t>
         </is>
       </c>
     </row>
@@ -880,46 +880,46 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>32,456,000</t>
+          <t>99,718,442</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>354,020,964</t>
+          <t>32,456,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -946,29 +946,29 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>99,718,442</t>
+          <t>354,020,964</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.66%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
@@ -1056,73 +1056,73 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>196,411,000</t>
+          <t>29,496,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>99,033,000</t>
+          <t>196,411,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>29,496,000</t>
+          <t>99,033,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -1188,46 +1188,46 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>272,189,000</t>
+          <t>53,388,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>53,388,000</t>
+          <t>272,189,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>10,452,302,226</t>
+          <t>10,491,334,913</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>7,078,310,311</t>
+          <t>6,953,231,911</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>-27,918,264</t>
+          <t>-9,102,080</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
